--- a/agile_documents/Defect_Tracker Template_v0.1.xlsx
+++ b/agile_documents/Defect_Tracker Template_v0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3DF93A8BBD052DAA/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC4EACBB-8F7A-4584-8E39-BBE80DB3A2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{EC4EACBB-8F7A-4584-8E39-BBE80DB3A2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FAB3497-6B10-4C9E-9347-8CF239DFD978}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>Sl No</t>
   </si>
@@ -80,129 +80,20 @@
     <t>Priyanka Dey</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Running the RAG engine script triggered a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>LangChainDeprecationWarning</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> because </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>langchain-community</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> HuggingFace embeddings were sunset</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The Streamlit web interface crashed with a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>NameError: name 'query_knowledge_base' is not defined</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> when attempting to search the knowledge base</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Installed the updated langchain-huggingface and langchain-chroma packages and replaced the old import statements in the backend script.   </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Carefully reviewed </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>app.py</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> and added the missing </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>from src.rag_engine import query_knowledge_base</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> import statement at the top of the file</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>The deprecation warnings are resolved and the vector database indexes successfully without pending package refresh errors.</t>
-  </si>
-  <si>
-    <t>Issue has been resolved and the user is able to retrieve security standards seamlessly from the search tab.</t>
+    <t>Encountered LangChain deprecation warnings during RAG ingestion and a NameError ('query_knowledge_base' / 'Chroma' / 'PERSIST_DIRECTORY' not defined) when querying the vector store in Streamlit.</t>
+  </si>
+  <si>
+    <t>Migrated to standalone packages (langchain-huggingface, langchain-text-splitters), defined global paths and imports in rag_engine.py, added @st.cache_resource for performance, and implemented result deduplication in app.py.</t>
+  </si>
+  <si>
+    <t>All import errors, missing paths, and deprecation warnings have been fully resolved; the RAG knowledge base runs efficiently and renders unique search results seamlessly.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -260,12 +151,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF003366"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Arial Unicode MS"/>
     </font>
@@ -311,12 +196,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -329,12 +211,6 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -342,6 +218,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -651,343 +539,321 @@
   <dimension ref="A1:K20"/>
   <sheetFormatPr defaultColWidth="17.5546875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="6.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.44140625" style="9" customWidth="1"/>
-    <col min="4" max="4" width="42.109375" style="9" customWidth="1"/>
-    <col min="5" max="5" width="16" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="21.88671875" style="9" customWidth="1"/>
-    <col min="11" max="11" width="16.88671875" style="9" customWidth="1"/>
-    <col min="12" max="16384" width="17.5546875" style="9"/>
+    <col min="1" max="1" width="6.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="42.109375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="16" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="21.88671875" style="6" customWidth="1"/>
+    <col min="11" max="11" width="16.88671875" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="17.5546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="4" customFormat="1" ht="31.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:11" s="3" customFormat="1" ht="31.2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="140.4">
-      <c r="A2" s="5">
+    <row r="2" spans="1:11" ht="145.19999999999999">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="6">
-        <v>46307</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="C2" s="5">
+        <v>46311</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="5">
+        <v>46311</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="6">
-        <v>46307</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="92.4">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="6">
-        <v>46308</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="6">
-        <v>46308</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>24</v>
-      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.6">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11" ht="15.6">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:11" ht="15.6">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
     </row>
     <row r="6" spans="1:11" ht="15.6">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
     </row>
     <row r="7" spans="1:11" ht="15.6">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="11"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:11" ht="15.6">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
     </row>
     <row r="9" spans="1:11" ht="15.6">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="11"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" spans="1:11" ht="15.6">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="11"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11" ht="15.6">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
     </row>
     <row r="12" spans="1:11" ht="15.6">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="11"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="8"/>
     </row>
     <row r="13" spans="1:11" ht="15.6">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
     </row>
     <row r="14" spans="1:11" ht="15.6">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="11"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="8"/>
     </row>
     <row r="15" spans="1:11" ht="15.6">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
     </row>
     <row r="16" spans="1:11" ht="15.6">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="11"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="8"/>
     </row>
     <row r="17" spans="1:11" ht="15.6">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="11"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="8"/>
     </row>
     <row r="18" spans="1:11" ht="15.6">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="11"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="8"/>
     </row>
     <row r="19" spans="1:11" ht="15.6">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
     </row>
     <row r="20" spans="1:11" ht="15.6">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="11"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1178,18 +1044,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1211,18 +1077,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20D196DE-5AC8-4D3B-8CD7-1A2AE6EEDD72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B149665-BEBB-4C97-BAA6-72374EAA67F9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20D196DE-5AC8-4D3B-8CD7-1A2AE6EEDD72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/agile_documents/Defect_Tracker Template_v0.1.xlsx
+++ b/agile_documents/Defect_Tracker Template_v0.1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3DF93A8BBD052DAA/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3df93a8bbd052daa/Desktop/Milestone 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="8_{EC4EACBB-8F7A-4584-8E39-BBE80DB3A2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FAB3497-6B10-4C9E-9347-8CF239DFD978}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{EC4EACBB-8F7A-4584-8E39-BBE80DB3A2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17ED926C-2465-4F53-B046-04E9CAE093DF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>Sl No</t>
   </si>
@@ -87,6 +87,35 @@
   </si>
   <si>
     <t>All import errors, missing paths, and deprecation warnings have been fully resolved; the RAG knowledge base runs efficiently and renders unique search results seamlessly.</t>
+  </si>
+  <si>
+    <t>Overlapping regex patterns between security and quality agents resulted in duplicate finding cards appearing on the same line.</t>
+  </si>
+  <si>
+    <t>Sprint 2</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implemented advanced line-grouping logic and severity merging inside </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>workflow.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to unify multi-agent issues cleanly.</t>
+    </r>
+  </si>
+  <si>
+    <t>Verified that all multi-agent findings now render uniquely with prioritized high severities per line.</t>
   </si>
 </sst>
 </file>
@@ -196,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -229,8 +258,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -247,6 +279,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -621,18 +657,40 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.6">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="12"/>
+    <row r="3" spans="1:11" ht="79.2">
+      <c r="A3" s="4">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="5">
+        <v>46323</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="5">
+        <v>46320</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="4" spans="1:11" ht="15.6">
       <c r="A4" s="4"/>
@@ -1044,18 +1102,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1077,18 +1135,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20D196DE-5AC8-4D3B-8CD7-1A2AE6EEDD72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B149665-BEBB-4C97-BAA6-72374EAA67F9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20D196DE-5AC8-4D3B-8CD7-1A2AE6EEDD72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>